--- a/new-info14 - a标签跳转/web.xlsx
+++ b/new-info14 - a标签跳转/web.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectInfo\new-info14\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectInfo\new-info14 - a标签跳转\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>domain</t>
   </si>
@@ -45,16 +45,10 @@
     <t>color2</t>
   </si>
   <si>
-    <t>read.roaddivider.cloud</t>
-  </si>
-  <si>
-    <t>#a48ce6</t>
-  </si>
-  <si>
-    <t>sec.roaddivider.cloud</t>
-  </si>
-  <si>
-    <t>#373834</t>
+    <t>read.roadstripe.cloud</t>
+  </si>
+  <si>
+    <t>#707899</t>
   </si>
   <si>
     <t>#f7ece7</t>
@@ -103,7 +97,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -120,7 +114,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -129,13 +123,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -326,7 +313,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA48CE6"/>
+        <fgColor rgb="FF707899"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,154 +736,157 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -905,46 +895,46 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1357,72 +1347,68 @@
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="I4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>8</v>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="I4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="7"/>
-      <c r="I5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>10</v>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="8"/>
+      <c r="I5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="11"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="12"/>
-      <c r="I6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>12</v>
+      <c r="A6" s="12"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="13"/>
+      <c r="I6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
-      <c r="B7" s="18"/>
-      <c r="C7" s="15"/>
-      <c r="I7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>14</v>
+      <c r="B7" s="19"/>
+      <c r="C7" s="16"/>
+      <c r="I7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="19"/>
-      <c r="I8" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="22" t="s">
-        <v>16</v>
+      <c r="B8" s="20"/>
+      <c r="I8" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="I9" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>18</v>
+      <c r="I9" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
